--- a/GameData/DataTables/Core/LanguagesTable.xlsx
+++ b/GameData/DataTables/Core/LanguagesTable.xlsx
@@ -8,9 +8,64 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>LanguagesTable</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>LanguageKey</t>
+  </si>
+  <si>
+    <t>AssetName</t>
+  </si>
+  <si>
+    <t>LanguageDisplay</t>
+  </si>
+  <si>
+    <t>LanguageIcon</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>多语言文件名</t>
+  </si>
+  <si>
+    <t>多语言资源名(相对路径)</t>
+  </si>
+  <si>
+    <t>用于显示的语言名</t>
+  </si>
+  <si>
+    <t>语言图标</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18,24 +73,24 @@
   <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -54,9 +109,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -395,7 +450,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable=" xr">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -403,151 +458,121 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="33.140625" customWidth="1" min="5" max="5"/>
-    <col width="17.140625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="28" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col min="4" max="4" bestFit="1" width="33.140625" customWidth="1"/>
+    <col min="5" max="5" width="33.140625" customWidth="1"/>
+    <col min="6" max="6" bestFit="1" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" bestFit="1" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>LanguagesTable</t>
-        </is>
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>LanguageKey</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>AssetName</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>LanguageDisplay</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>LanguageIcon</t>
-        </is>
+      <c r="A2" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+      <c r="A3" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>多语言文件名</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>多语言资源名(相对路径)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>用于显示的语言名</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>语言图标</t>
-        </is>
+      <c r="A4" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
+      <c r="A5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D3:AA3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D3:AA3" xr:uid="{55A92C0B-228B-427D-ACFF-311B32D2A96B}">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <headerFooter/>
 </worksheet>
 </file>